--- a/test_results/gemini_2_5_flash_preview_09_2025/统计表格.xlsx
+++ b/test_results/gemini_2_5_flash_preview_09_2025/统计表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\111\新建文件夹\数据分析\分析结果\gemini_2_5_flash_preview_09_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\111\LLM-NeedleInAHaystack\test_results\gemini_2_5_flash_preview_09_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9270440F-AC6D-4629-8EE6-CFC27F265236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE992CD2-15FB-4F14-8313-95916EAC4F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{58898F7C-67C2-4EC0-A511-F699C1A6044A}"/>
+    <workbookView xWindow="1390" yWindow="770" windowWidth="21200" windowHeight="13630" xr2:uid="{58898F7C-67C2-4EC0-A511-F699C1A6044A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -308,37 +308,37 @@
                   <c:v>99.79</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.08</c:v>
+                  <c:v>97.94</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.96</c:v>
+                  <c:v>94.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70.8</c:v>
+                  <c:v>85.68</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.27</c:v>
+                  <c:v>67.31</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28.74</c:v>
+                  <c:v>49.84</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.37</c:v>
+                  <c:v>25.45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.48</c:v>
+                  <c:v>24.86</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.55</c:v>
+                  <c:v>17.559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.4</c:v>
+                  <c:v>7.81</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.02</c:v>
+                  <c:v>6.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1399999999999999</c:v>
+                  <c:v>4.7699999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1493,37 +1493,37 @@
                   <c:v>99.79</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.08</c:v>
+                  <c:v>97.94</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.96</c:v>
+                  <c:v>94.15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70.8</c:v>
+                  <c:v>85.68</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>48.27</c:v>
+                  <c:v>67.31</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28.74</c:v>
+                  <c:v>49.84</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.37</c:v>
+                  <c:v>25.45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.48</c:v>
+                  <c:v>24.86</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.55</c:v>
+                  <c:v>17.559999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.4</c:v>
+                  <c:v>7.81</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.02</c:v>
+                  <c:v>6.83</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.1399999999999999</c:v>
+                  <c:v>4.7699999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4073,37 +4073,37 @@
         <v>99.79</v>
       </c>
       <c r="C8">
-        <v>97.08</v>
+        <v>97.94</v>
       </c>
       <c r="D8">
-        <v>88.96</v>
+        <v>94.15</v>
       </c>
       <c r="E8">
-        <v>70.8</v>
+        <v>85.68</v>
       </c>
       <c r="F8">
-        <v>48.27</v>
+        <v>67.31</v>
       </c>
       <c r="G8">
-        <v>28.74</v>
+        <v>49.84</v>
       </c>
       <c r="H8">
-        <v>7.37</v>
+        <v>25.45</v>
       </c>
       <c r="I8">
-        <v>8.48</v>
+        <v>24.86</v>
       </c>
       <c r="J8">
-        <v>5.55</v>
+        <v>17.559999999999999</v>
       </c>
       <c r="K8">
-        <v>2.4</v>
+        <v>7.81</v>
       </c>
       <c r="L8">
-        <v>2.02</v>
+        <v>6.83</v>
       </c>
       <c r="M8">
-        <v>1.1399999999999999</v>
+        <v>4.7699999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
